--- a/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:07:35+00:00</t>
+    <t>2026-06-16T13:33:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:33:17+00:00</t>
+    <t>2026-06-16T14:03:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:03:43+00:00</t>
+    <t>2026-06-16T14:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:16:24+00:00</t>
+    <t>2026-06-16T15:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T15:20:57+00:00</t>
+    <t>2026-06-16T16:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/patch/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:25:55+00:00</t>
+    <t>2026-06-17T07:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
